--- a/en/downloads/data-excel/1.5.4.xlsx
+++ b/en/downloads/data-excel/1.5.4.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC1F455-62AA-4A34-96C2-9BD1E71037F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -83,7 +84,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _р_._-;\-* #,##0.00\ _р_._-;_-* &quot;-&quot;??\ _р_._-;_-@_-"/>
@@ -290,91 +291,85 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="24">
-    <cellStyle name="40% — акцент2 2" xfId="22"/>
-    <cellStyle name="Normal 17" xfId="18"/>
-    <cellStyle name="Normal 2" xfId="21"/>
-    <cellStyle name="Normal_Sheet1 2" xfId="23"/>
+    <cellStyle name="40% — акцент2 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal 17" xfId="18" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal_Sheet1 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 10" xfId="2"/>
-    <cellStyle name="Обычный 11" xfId="20"/>
-    <cellStyle name="Обычный 2" xfId="3"/>
-    <cellStyle name="Обычный 2 2" xfId="4"/>
-    <cellStyle name="Обычный 2 3" xfId="5"/>
-    <cellStyle name="Обычный 3" xfId="6"/>
-    <cellStyle name="Обычный 3 2" xfId="7"/>
-    <cellStyle name="Обычный 4" xfId="8"/>
-    <cellStyle name="Обычный 5" xfId="9"/>
-    <cellStyle name="Обычный 6" xfId="1"/>
-    <cellStyle name="Обычный 7" xfId="19"/>
-    <cellStyle name="Обычный 8" xfId="10"/>
-    <cellStyle name="Обычный 9" xfId="11"/>
-    <cellStyle name="Пояснение 2" xfId="12"/>
-    <cellStyle name="Процентный 2" xfId="13"/>
-    <cellStyle name="Процентный 3" xfId="14"/>
-    <cellStyle name="Стиль 1" xfId="15"/>
-    <cellStyle name="Финансовый 2" xfId="16"/>
-    <cellStyle name="Финансовый 3" xfId="17"/>
+    <cellStyle name="Обычный 10" xfId="2" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Обычный 11" xfId="20" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Обычный 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Обычный 2 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Обычный 3" xfId="6" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Обычный 3 2" xfId="7" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Обычный 4" xfId="8" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Обычный 5" xfId="9" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Обычный 6" xfId="1" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Обычный 7" xfId="19" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Обычный 8" xfId="10" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Обычный 9" xfId="11" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Пояснение 2" xfId="12" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Процентный 2" xfId="13" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Процентный 3" xfId="14" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Стиль 1" xfId="15" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Финансовый 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Финансовый 3" xfId="17" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -390,7 +385,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Data"/>
@@ -8116,18 +8111,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="41.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="82.5" customHeight="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:9" ht="82.5" customHeight="1">
+      <c r="A1" s="12" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -8137,12 +8132,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A2" s="15"/>
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A2" s="13"/>
       <c r="B2" s="4"/>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A3" s="16" t="s">
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A3" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -8166,83 +8161,95 @@
       <c r="H3" s="2">
         <v>2023</v>
       </c>
+      <c r="I3" s="2">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" ht="19.5" customHeight="1">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:9" ht="19.5" customHeight="1">
+      <c r="A4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="10">
         <v>484</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="10">
         <v>484</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="10">
         <v>484</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="10">
         <v>484</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="10">
+        <v>484</v>
+      </c>
+      <c r="I4" s="10">
         <v>484</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="44.25" customHeight="1">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:9" ht="44.25" customHeight="1">
+      <c r="A5" s="16" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="11">
         <v>10.12397</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="11">
         <v>13.2</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="11">
         <v>21.5</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="11">
         <v>34.5</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="11">
         <v>40.53</v>
       </c>
+      <c r="I5" s="11">
+        <v>35.5</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" ht="51.75" customHeight="1" thickBot="1">
-      <c r="A6" s="19" t="s">
+    <row r="6" spans="1:9" ht="51.75" customHeight="1" thickBot="1">
+      <c r="A6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="7">
         <v>49</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="7">
         <v>67</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="7">
         <v>104</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="7">
         <v>167</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="7">
         <v>169</v>
+      </c>
+      <c r="I6" s="7">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
